--- a/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\EVALUACIONES\MOVILIDAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E01990-F5B8-4334-BE97-0BCC60D94C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>Fecha</t>
   </si>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>rodrigo_cueva</t>
-  </si>
-  <si>
-    <t>LUMBAR</t>
   </si>
 </sst>
 </file>
@@ -217,9 +214,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:I53" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:I53" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:H53" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:H53" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
     <tableColumn id="14" xr3:uid="{D727A1D4-7598-4A63-8792-0A263635CB77}" name="DORSIFLEX_D"/>
@@ -228,7 +225,6 @@
     <tableColumn id="17" xr3:uid="{8CAEDC32-16A2-44F0-A7E9-B9025E226A48}" name="ROT_INT_I"/>
     <tableColumn id="18" xr3:uid="{2B266D09-B02D-45A4-98C0-E0D66D95B3FE}" name="FLEX_CAD_D"/>
     <tableColumn id="19" xr3:uid="{22F77E7A-F5A6-4713-91E5-11305A5C93A6}" name="FLEX_CAD_I"/>
-    <tableColumn id="3" xr3:uid="{B6E03D75-C271-4274-A2D9-819044AFE11E}" name="LUMBAR"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -531,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -543,7 +539,7 @@
     <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,11 +564,8 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46569</v>
       </c>
@@ -597,11 +590,8 @@
       <c r="H2">
         <v>95</v>
       </c>
-      <c r="I2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46569</v>
       </c>
@@ -626,11 +616,8 @@
       <c r="H3">
         <v>95</v>
       </c>
-      <c r="I3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46569</v>
       </c>
@@ -655,11 +642,8 @@
       <c r="H4">
         <v>95</v>
       </c>
-      <c r="I4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46569</v>
       </c>
@@ -684,11 +668,8 @@
       <c r="H5">
         <v>95</v>
       </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46569</v>
       </c>
@@ -713,11 +694,8 @@
       <c r="H6">
         <v>95</v>
       </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46569</v>
       </c>
@@ -742,11 +720,8 @@
       <c r="H7">
         <v>95</v>
       </c>
-      <c r="I7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46569</v>
       </c>
@@ -771,11 +746,8 @@
       <c r="H8">
         <v>95</v>
       </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46569</v>
       </c>
@@ -800,11 +772,8 @@
       <c r="H9">
         <v>95</v>
       </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46569</v>
       </c>
@@ -829,11 +798,8 @@
       <c r="H10">
         <v>95</v>
       </c>
-      <c r="I10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46569</v>
       </c>
@@ -858,11 +824,8 @@
       <c r="H11">
         <v>95</v>
       </c>
-      <c r="I11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46569</v>
       </c>
@@ -887,11 +850,8 @@
       <c r="H12">
         <v>95</v>
       </c>
-      <c r="I12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46569</v>
       </c>
@@ -916,11 +876,8 @@
       <c r="H13">
         <v>95</v>
       </c>
-      <c r="I13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46569</v>
       </c>
@@ -945,11 +902,8 @@
       <c r="H14">
         <v>95</v>
       </c>
-      <c r="I14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46569</v>
       </c>
@@ -974,11 +928,8 @@
       <c r="H15">
         <v>95</v>
       </c>
-      <c r="I15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46569</v>
       </c>
@@ -1003,11 +954,8 @@
       <c r="H16">
         <v>95</v>
       </c>
-      <c r="I16">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46569</v>
       </c>
@@ -1032,11 +980,8 @@
       <c r="H17">
         <v>95</v>
       </c>
-      <c r="I17">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46569</v>
       </c>
@@ -1061,11 +1006,8 @@
       <c r="H18">
         <v>95</v>
       </c>
-      <c r="I18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46569</v>
       </c>
@@ -1090,11 +1032,8 @@
       <c r="H19">
         <v>95</v>
       </c>
-      <c r="I19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46569</v>
       </c>
@@ -1119,11 +1058,8 @@
       <c r="H20">
         <v>95</v>
       </c>
-      <c r="I20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46569</v>
       </c>
@@ -1148,11 +1084,8 @@
       <c r="H21">
         <v>95</v>
       </c>
-      <c r="I21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46569</v>
       </c>
@@ -1177,11 +1110,8 @@
       <c r="H22">
         <v>95</v>
       </c>
-      <c r="I22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46569</v>
       </c>
@@ -1206,11 +1136,8 @@
       <c r="H23">
         <v>95</v>
       </c>
-      <c r="I23">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46569</v>
       </c>
@@ -1235,11 +1162,8 @@
       <c r="H24">
         <v>95</v>
       </c>
-      <c r="I24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46569</v>
       </c>
@@ -1264,11 +1188,8 @@
       <c r="H25">
         <v>95</v>
       </c>
-      <c r="I25">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46569</v>
       </c>
@@ -1293,11 +1214,8 @@
       <c r="H26">
         <v>95</v>
       </c>
-      <c r="I26">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46569</v>
       </c>
@@ -1322,11 +1240,8 @@
       <c r="H27">
         <v>95</v>
       </c>
-      <c r="I27">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46632</v>
       </c>
@@ -1351,11 +1266,8 @@
       <c r="H28">
         <v>12</v>
       </c>
-      <c r="I28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46632</v>
       </c>
@@ -1380,11 +1292,8 @@
       <c r="H29">
         <v>10</v>
       </c>
-      <c r="I29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46632</v>
       </c>
@@ -1409,11 +1318,8 @@
       <c r="H30">
         <v>9</v>
       </c>
-      <c r="I30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46632</v>
       </c>
@@ -1438,11 +1344,8 @@
       <c r="H31">
         <v>12</v>
       </c>
-      <c r="I31">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46632</v>
       </c>
@@ -1467,11 +1370,8 @@
       <c r="H32">
         <v>10</v>
       </c>
-      <c r="I32">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46632</v>
       </c>
@@ -1496,11 +1396,8 @@
       <c r="H33">
         <v>9</v>
       </c>
-      <c r="I33">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46632</v>
       </c>
@@ -1525,11 +1422,8 @@
       <c r="H34">
         <v>12</v>
       </c>
-      <c r="I34">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46632</v>
       </c>
@@ -1554,11 +1448,8 @@
       <c r="H35">
         <v>10</v>
       </c>
-      <c r="I35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46632</v>
       </c>
@@ -1583,11 +1474,8 @@
       <c r="H36">
         <v>9</v>
       </c>
-      <c r="I36">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46632</v>
       </c>
@@ -1612,11 +1500,8 @@
       <c r="H37">
         <v>12</v>
       </c>
-      <c r="I37">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46632</v>
       </c>
@@ -1641,11 +1526,8 @@
       <c r="H38">
         <v>10</v>
       </c>
-      <c r="I38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46632</v>
       </c>
@@ -1670,11 +1552,8 @@
       <c r="H39">
         <v>9</v>
       </c>
-      <c r="I39">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46632</v>
       </c>
@@ -1699,11 +1578,8 @@
       <c r="H40">
         <v>10</v>
       </c>
-      <c r="I40">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46632</v>
       </c>
@@ -1728,11 +1604,8 @@
       <c r="H41">
         <v>10</v>
       </c>
-      <c r="I41">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46632</v>
       </c>
@@ -1757,11 +1630,8 @@
       <c r="H42">
         <v>10</v>
       </c>
-      <c r="I42">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46632</v>
       </c>
@@ -1786,11 +1656,8 @@
       <c r="H43">
         <v>12</v>
       </c>
-      <c r="I43">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46632</v>
       </c>
@@ -1815,11 +1682,8 @@
       <c r="H44">
         <v>10</v>
       </c>
-      <c r="I44">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46632</v>
       </c>
@@ -1844,11 +1708,8 @@
       <c r="H45">
         <v>9</v>
       </c>
-      <c r="I45">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46632</v>
       </c>
@@ -1873,11 +1734,8 @@
       <c r="H46">
         <v>10</v>
       </c>
-      <c r="I46">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46632</v>
       </c>
@@ -1902,11 +1760,8 @@
       <c r="H47">
         <v>10</v>
       </c>
-      <c r="I47">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46632</v>
       </c>
@@ -1931,11 +1786,8 @@
       <c r="H48">
         <v>12</v>
       </c>
-      <c r="I48">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46632</v>
       </c>
@@ -1960,11 +1812,8 @@
       <c r="H49">
         <v>10</v>
       </c>
-      <c r="I49">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46632</v>
       </c>
@@ -1989,11 +1838,8 @@
       <c r="H50">
         <v>9</v>
       </c>
-      <c r="I50">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46632</v>
       </c>
@@ -2018,11 +1864,8 @@
       <c r="H51">
         <v>12</v>
       </c>
-      <c r="I51">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46632</v>
       </c>
@@ -2047,11 +1890,8 @@
       <c r="H52">
         <v>10</v>
       </c>
-      <c r="I52">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46632</v>
       </c>
@@ -2074,9 +1914,6 @@
         <v>9</v>
       </c>
       <c r="H53">
-        <v>9</v>
-      </c>
-      <c r="I53">
         <v>9</v>
       </c>
     </row>

--- a/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BD51260-F4B4-45B0-93ED-27DE4E0958C2}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33AF7B49-C284-4AC8-87C1-B086FF6AA2A5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -525,18 +525,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,31 +562,85 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46247</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <v>8.5</v>
+      </c>
+      <c r="D2">
+        <v>7.7</v>
+      </c>
+      <c r="E2">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="F2">
+        <v>51.2</v>
+      </c>
+      <c r="G2">
+        <v>81.8</v>
+      </c>
+      <c r="H2">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46247</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>10.5</v>
+      </c>
+      <c r="D3">
+        <v>9.5</v>
+      </c>
+      <c r="E3">
+        <v>36.1</v>
+      </c>
+      <c r="F3">
+        <v>33.5</v>
+      </c>
+      <c r="G3">
+        <v>75.3</v>
+      </c>
+      <c r="H3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46247</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>10.5</v>
+      </c>
+      <c r="D4">
+        <v>11.5</v>
+      </c>
+      <c r="E4">
+        <v>46</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="H4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46247</v>
       </c>
@@ -612,15 +666,33 @@
         <v>70.7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46247</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>6.8</v>
+      </c>
+      <c r="D6">
+        <v>7.8</v>
+      </c>
+      <c r="E6">
+        <v>31.6</v>
+      </c>
+      <c r="F6">
+        <v>28.6</v>
+      </c>
+      <c r="G6">
+        <v>71.8</v>
+      </c>
+      <c r="H6">
+        <v>73.099999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46247</v>
       </c>
@@ -646,7 +718,7 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46247</v>
       </c>
@@ -672,7 +744,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46247</v>
       </c>
@@ -698,15 +770,33 @@
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46247</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <v>10.8</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>30.2</v>
+      </c>
+      <c r="G10">
+        <v>71.8</v>
+      </c>
+      <c r="H10">
+        <v>77.900000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46247</v>
       </c>
@@ -732,39 +822,111 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46247</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>6.5</v>
+      </c>
+      <c r="E12">
+        <v>30.7</v>
+      </c>
+      <c r="F12">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="H12">
+        <v>71.099999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46247</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>30.8</v>
+      </c>
+      <c r="G13">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="H13">
+        <v>80.900000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46247</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>3.9</v>
+      </c>
+      <c r="E14">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F14">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G14">
+        <v>69.3</v>
+      </c>
+      <c r="H14">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46247</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>9.5</v>
+      </c>
+      <c r="E15">
+        <v>44.6</v>
+      </c>
+      <c r="F15">
+        <v>44.4</v>
+      </c>
+      <c r="G15">
+        <v>86.4</v>
+      </c>
+      <c r="H15">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46247</v>
       </c>
@@ -772,7 +934,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46247</v>
       </c>
@@ -780,7 +942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46247</v>
       </c>
@@ -788,7 +950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46247</v>
       </c>
@@ -796,7 +958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46247</v>
       </c>
@@ -804,7 +966,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46247</v>
       </c>
@@ -830,7 +992,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46247</v>
       </c>
@@ -856,7 +1018,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46247</v>
       </c>
@@ -864,7 +1026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>46247</v>
       </c>
@@ -872,7 +1034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46247</v>
       </c>
@@ -880,7 +1042,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46247</v>
       </c>

--- a/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33AF7B49-C284-4AC8-87C1-B086FF6AA2A5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B4B6C6F-1886-4D83-8074-A3BA3CCA9681}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -525,18 +525,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46247</v>
       </c>
@@ -588,7 +588,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46247</v>
       </c>
@@ -614,7 +614,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46247</v>
       </c>
@@ -640,7 +640,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46247</v>
       </c>
@@ -666,7 +666,7 @@
         <v>70.7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46247</v>
       </c>
@@ -692,7 +692,7 @@
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46247</v>
       </c>
@@ -718,7 +718,7 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46247</v>
       </c>
@@ -744,7 +744,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46247</v>
       </c>
@@ -770,7 +770,7 @@
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46247</v>
       </c>
@@ -796,7 +796,7 @@
         <v>77.900000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46247</v>
       </c>
@@ -822,7 +822,7 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46247</v>
       </c>
@@ -848,7 +848,7 @@
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46247</v>
       </c>
@@ -874,7 +874,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46247</v>
       </c>
@@ -900,7 +900,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46247</v>
       </c>
@@ -926,47 +926,137 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46247</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>29.3</v>
+      </c>
+      <c r="F16">
+        <v>29.8</v>
+      </c>
+      <c r="G16">
+        <v>69.7</v>
+      </c>
+      <c r="H16">
+        <v>69.400000000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46247</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>10.5</v>
+      </c>
+      <c r="E17">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F17">
+        <v>36.6</v>
+      </c>
+      <c r="G17">
+        <v>67.3</v>
+      </c>
+      <c r="H17">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46247</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <v>17.5</v>
+      </c>
+      <c r="D18">
+        <v>17.5</v>
+      </c>
+      <c r="E18">
+        <v>50.2</v>
+      </c>
+      <c r="F18">
+        <v>47.8</v>
+      </c>
+      <c r="G18">
+        <v>82.6</v>
+      </c>
+      <c r="H18">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46247</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C19">
+        <v>6.5</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>26</v>
+      </c>
+      <c r="F19">
+        <v>26.1</v>
+      </c>
+      <c r="G19">
+        <v>70</v>
+      </c>
+      <c r="H19">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46247</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E20">
+        <v>28.9</v>
+      </c>
+      <c r="F20">
+        <v>26.3</v>
+      </c>
+      <c r="G20">
+        <v>76.7</v>
+      </c>
+      <c r="H20">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46247</v>
       </c>
@@ -992,7 +1082,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46247</v>
       </c>
@@ -1018,31 +1108,85 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46247</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C23">
+        <v>5.9</v>
+      </c>
+      <c r="D23">
+        <v>5.5</v>
+      </c>
+      <c r="E23">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="F23">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="G23">
+        <v>80.2</v>
+      </c>
+      <c r="H23">
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46247</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C24">
+        <v>4.5</v>
+      </c>
+      <c r="D24">
+        <v>3.8</v>
+      </c>
+      <c r="E24">
+        <v>54</v>
+      </c>
+      <c r="F24">
+        <v>60.4</v>
+      </c>
+      <c r="G24">
+        <v>72.2</v>
+      </c>
+      <c r="H24">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46247</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C25">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>9.5</v>
+      </c>
+      <c r="E25">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>25</v>
+      </c>
+      <c r="G25">
+        <v>61.9</v>
+      </c>
+      <c r="H25">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46247</v>
       </c>

--- a/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B4B6C6F-1886-4D83-8074-A3BA3CCA9681}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BC7C68-6FD2-4C53-9E4C-7454E9485E81}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -117,13 +117,13 @@
     <t>Petko_Avramov</t>
   </si>
   <si>
-    <t>Jaime_Muñoz_Garcia</t>
-  </si>
-  <si>
     <t>Jorge_vicaria</t>
   </si>
   <si>
     <t>Juan_Manuel_Ruiz</t>
+  </si>
+  <si>
+    <t>Jaime_Munoz_Garcia</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1139,7 @@
         <v>46247</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -1165,7 +1165,7 @@
         <v>46247</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -1191,7 +1191,7 @@
         <v>46247</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>7</v>

--- a/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BC7C68-6FD2-4C53-9E4C-7454E9485E81}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1DFFC70-40D4-4F75-A416-4F8AB0C9B457}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -211,8 +211,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:H26" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:H26" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:H27" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:H27" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -524,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1212,6 +1212,11 @@
         <v>83</v>
       </c>
     </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
